--- a/resources/templates/standard/M4100-02.xlsx
+++ b/resources/templates/standard/M4100-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>현장용 3정 5행 진단 SHEET</t>
   </si>
@@ -771,12 +774,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -797,20 +802,20 @@
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4"/>
       <c r="AE1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
@@ -887,7 +892,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -913,24 +918,24 @@
       <c r="W4" s="7"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z4" s="5"/>
       <c r="AA4" s="5"/>
       <c r="AB4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
       <c r="AE4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF4" s="5"/>
       <c r="AG4" s="5"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -948,7 +953,7 @@
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
@@ -969,7 +974,7 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -1006,21 +1011,21 @@
     </row>
     <row r="7" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
@@ -1033,11 +1038,11 @@
       <c r="R7" s="12"/>
       <c r="S7" s="12"/>
       <c r="T7" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U7" s="12"/>
       <c r="V7" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W7" s="12"/>
       <c r="X7" s="12"/>
@@ -1053,11 +1058,11 @@
     </row>
     <row r="8" ht="23.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15">
@@ -1069,7 +1074,7 @@
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
@@ -1108,7 +1113,7 @@
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9" s="18"/>
       <c r="K9" s="18"/>
@@ -1147,7 +1152,7 @@
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" s="18"/>
       <c r="K10" s="18"/>
@@ -1186,7 +1191,7 @@
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
@@ -1225,7 +1230,7 @@
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J12" s="19"/>
       <c r="K12" s="19"/>
@@ -1256,7 +1261,7 @@
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="15">
@@ -1268,7 +1273,7 @@
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J13" s="16"/>
       <c r="K13" s="16"/>
@@ -1307,7 +1312,7 @@
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J14" s="18"/>
       <c r="K14" s="18"/>
@@ -1346,7 +1351,7 @@
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J15" s="18"/>
       <c r="K15" s="18"/>
@@ -1385,7 +1390,7 @@
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
@@ -1424,7 +1429,7 @@
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J17" s="19"/>
       <c r="K17" s="19"/>
@@ -1455,7 +1460,7 @@
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="15">
@@ -1467,7 +1472,7 @@
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
@@ -1506,7 +1511,7 @@
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J19" s="18"/>
       <c r="K19" s="18"/>
@@ -1545,7 +1550,7 @@
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -1584,7 +1589,7 @@
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
@@ -1623,7 +1628,7 @@
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J22" s="19"/>
       <c r="K22" s="19"/>
@@ -1654,7 +1659,7 @@
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="15">
@@ -1666,7 +1671,7 @@
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J23" s="16"/>
       <c r="K23" s="16"/>
@@ -1705,7 +1710,7 @@
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J24" s="18"/>
       <c r="K24" s="18"/>
@@ -1744,7 +1749,7 @@
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J25" s="18"/>
       <c r="K25" s="18"/>
@@ -1783,7 +1788,7 @@
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
@@ -1822,7 +1827,7 @@
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
@@ -1853,7 +1858,7 @@
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="15">
@@ -1865,7 +1870,7 @@
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J28" s="20"/>
       <c r="K28" s="20"/>
@@ -1904,7 +1909,7 @@
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J29" s="18"/>
       <c r="K29" s="18"/>
@@ -1943,7 +1948,7 @@
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J30" s="18"/>
       <c r="K30" s="18"/>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J31" s="18"/>
       <c r="K31" s="18"/>
@@ -2021,7 +2026,7 @@
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J32" s="21"/>
       <c r="K32" s="21"/>
@@ -2050,7 +2055,7 @@
     </row>
     <row r="33" ht="23.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
